--- a/stories/arbres/TREE-AUT-036.xlsx
+++ b/stories/arbres/TREE-AUT-036.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Zoé est avec maman, dans la chambre. Zoé a envie de jouer. maman est là, tout près. On va apprendre : Préparer son sac. Voici le geste : mettre dans le sac. Zoé écoute maman. Zoé entend les mots : sac, ce que l'adulte a dit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Zoé va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Zoé se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tait une seconde. maman dit : je suis là. On reste ensemble.</t>
+          <t>Zoé va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Zoé se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tait une seconde. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Zoé se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tait une seconde.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Zoé respire. Zoé retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2586,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2755,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. La lumière est claire. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3757,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3950,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4119,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4286,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4453,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4620,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4787,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4954,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5121,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5314,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5483,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5650,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5817,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5984,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6151,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6318,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6179,7 +6347,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Zoé va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Zoé se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tient la main. maman dit : je suis là. On reste ensemble.</t>
+          <t>Zoé va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Zoé se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tient la main. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6317,6 +6485,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Zoé se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tient la main.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6671,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6844,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Zoé respire. Zoé retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6851,6 +7035,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7013,6 +7202,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7201,6 +7395,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7365,6 +7564,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. La lumière est claire. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7731,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7898,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8065,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8232,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8399,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8566,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8759,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8928,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9095,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9262,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le toboggan, le seau et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9429,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9337,6 +9596,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9763,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9661,6 +9930,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9849,6 +10123,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10013,6 +10292,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10459,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10626,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10793,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10960,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11127,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10847,7 +11156,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Zoé va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Zoé se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On range un objet. maman dit : je suis là. On reste ensemble.</t>
+          <t>Zoé va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Zoé se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10985,6 +11294,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Zoé se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On range un objet.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11480,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11653,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Zoé respire. Zoé retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11519,6 +11844,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11681,6 +12011,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11869,6 +12204,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12033,6 +12373,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12195,6 +12540,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12357,6 +12707,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12519,6 +12874,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12681,6 +13041,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12843,6 +13208,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13005,6 +13375,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13193,6 +13568,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13357,6 +13737,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de les balançoires, le seau et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13519,6 +13904,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13681,6 +14071,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de les balançoires, le seau et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13843,6 +14238,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14005,6 +14405,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14167,6 +14572,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14329,6 +14739,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14517,6 +14932,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14681,6 +15101,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14843,6 +15268,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15005,6 +15435,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15167,6 +15602,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15329,6 +15769,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15491,6 +15936,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15509,7 +15959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15582,6 +16032,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-036.xlsx
+++ b/stories/arbres/TREE-AUT-036.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Zoé est avec maman, dans la chambre. Zoé a envie de jouer. maman est là, tout près. On va apprendre : Préparer son sac. Voici le geste : mettre dans le sac. Zoé écoute maman. Zoé entend les mots : sac, ce que l'adulte a dit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans le sac. Zoé respire. Zoé retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Zoé a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2773,7 @@
           <t>narrateur|Zoé rejoint Tom. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3109,7 @@
           <t>narrateur|Zoé rejoint Léa. La lumière est claire. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3445,7 @@
           <t>narrateur|Zoé rejoint Sami. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3781,7 @@
           <t>narrateur|Zoé a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3957,6 +3977,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
           <t>narrateur|Zoé rejoint Tom. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4481,7 @@
           <t>narrateur|Zoé rejoint Léa. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4817,7 @@
           <t>narrateur|Zoé rejoint Sami. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4985,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5153,7 @@
           <t>narrateur|Zoé a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5321,6 +5349,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5488,6 +5517,7 @@
           <t>narrateur|Zoé rejoint Tom. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5655,6 +5685,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5822,6 +5853,7 @@
           <t>narrateur|Zoé rejoint Léa. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5989,6 +6021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6156,6 +6189,7 @@
           <t>narrateur|Zoé rejoint Sami. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6323,6 +6357,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6491,6 +6526,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6678,6 +6714,7 @@
           <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6849,6 +6886,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans le sac. Zoé respire. Zoé retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7040,6 +7078,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7207,6 +7246,7 @@
           <t>narrateur|Zoé a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7402,6 +7442,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7569,6 +7610,7 @@
           <t>narrateur|Zoé rejoint Tom. La lumière est claire. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7736,6 +7778,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7903,6 +7946,7 @@
           <t>narrateur|Zoé rejoint Léa. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8070,6 +8114,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8237,6 +8282,7 @@
           <t>narrateur|Zoé rejoint Sami. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8404,6 +8450,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8571,6 +8618,7 @@
           <t>narrateur|Zoé a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8766,6 +8814,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8933,6 +8982,7 @@
           <t>narrateur|Zoé rejoint Tom. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9100,6 +9150,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9267,6 +9318,7 @@
           <t>narrateur|Zoé rejoint Léa. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le toboggan, le seau et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9434,6 +9486,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9601,6 +9654,7 @@
           <t>narrateur|Zoé rejoint Sami. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9768,6 +9822,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9935,6 +9990,7 @@
           <t>narrateur|Zoé a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10130,6 +10186,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10297,6 +10354,7 @@
           <t>narrateur|Zoé rejoint Tom. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10464,6 +10522,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10631,6 +10690,7 @@
           <t>narrateur|Zoé rejoint Léa. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10798,6 +10858,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10965,6 +11026,7 @@
           <t>narrateur|Zoé rejoint Sami. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11132,6 +11194,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11300,6 +11363,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11487,6 +11551,7 @@
           <t>narrateur|Que fait-on ? Préparer son sac.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11658,6 +11723,7 @@
           <t>narrateur|Oui. Voici le geste : mettre dans le sac. Zoé respire. Zoé retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11849,6 +11915,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12016,6 +12083,7 @@
           <t>narrateur|Zoé a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12211,6 +12279,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12378,6 +12447,7 @@
           <t>narrateur|Zoé rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12545,6 +12615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12712,6 +12783,7 @@
           <t>narrateur|Zoé rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12879,6 +12951,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13046,6 +13119,7 @@
           <t>narrateur|Zoé rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13213,6 +13287,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13380,6 +13455,7 @@
           <t>narrateur|Zoé a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13575,6 +13651,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13742,6 +13819,7 @@
           <t>narrateur|Zoé rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de les balançoires, le seau et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13909,6 +13987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14076,6 +14155,7 @@
           <t>narrateur|Zoé rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de les balançoires, le seau et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14243,6 +14323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14410,6 +14491,7 @@
           <t>narrateur|Zoé rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14577,6 +14659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14744,6 +14827,7 @@
           <t>narrateur|Zoé a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14939,6 +15023,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15106,6 +15191,7 @@
           <t>narrateur|Zoé rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15273,6 +15359,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15440,6 +15527,7 @@
           <t>narrateur|Zoé rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15607,6 +15695,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15774,6 +15863,7 @@
           <t>narrateur|Zoé rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15941,6 +16031,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15959,7 +16050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16039,6 +16130,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16053,7 +16158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16240,6 +16345,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-036.xlsx
+++ b/stories/arbres/TREE-AUT-036.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Préparer son sac — dans la chambre</t>
+          <t>L'oiseau de papier et le sac rouge de Sarah</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un oiseau en papier tourne dans la chambre. Sarah veut jouer. Avant, on met dans le sac ce que papa ou maman a dit.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Zoé est avec maman, dans la chambre. Zoé a envie de jouer. maman est là, tout près. On va apprendre : Préparer son sac. Voici le geste : mettre dans le sac. Zoé écoute maman. Zoé entend les mots : sac, ce que l'adulte a dit.</t>
+          <t>Un oiseau en papier tourne sous le plafond. Il est blanc, un peu froissé. Le fil fait un petit cercle lent. Les rideaux ont des lunes bleues. Un rayon passe entre deux lunes. La poussière danse, toute fine. Une chaussette jaune dort sur la lampe. Le lit est encore chaud, un peu en vrac. Ça sent le savon de la lessive. Le sac rouge est au pied du lit. Les sangles pendent, molles. Papa plie un pull à étoile. Maman cherche un petit livre. Tu as vu l'oiseau, Sarah ? Oui. Il tourne. Ton sac t'attend, tout en bas. En ce moment, Sarah touche le sac. Le tissu est un peu rêche. Je veux jouer ! D'accord. On prépare le sac d'abord. On met dans le sac ce que maman a dit. Ou ce que papa a dit. J'écoute. Oui. On met ce que l'adulte a dit. L'oiseau en papier tourne encore. La chaussette jaune ne bouge pas.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,7 +1337,32 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Zoé est avec maman, dans la chambre. Zoé a envie de jouer. maman est là, tout près. On va apprendre : Préparer son sac. Voici le geste : mettre dans le sac. Zoé écoute maman. Zoé entend les mots : sac, ce que l'adulte a dit.</t>
+          <t>narrateur|Un oiseau en papier tourne sous le plafond.
+narrateur|Il est blanc, un peu froissé.
+narrateur|Le fil fait un petit cercle lent.
+narrateur|Les rideaux ont des lunes bleues.
+narrateur|Un rayon passe entre deux lunes.
+narrateur|La poussière danse, toute fine.
+narrateur|Une chaussette jaune dort sur la lampe.
+narrateur|Le lit est encore chaud, un peu en vrac.
+narrateur|Ça sent le savon de la lessive.
+narrateur|Le sac rouge est au pied du lit.
+narrateur|Les sangles pendent, molles.
+narrateur|Papa plie un pull à étoile.
+narrateur|Maman cherche un petit livre.
+maman|Tu as vu l'oiseau, Sarah ?
+enfant-f|Oui. Il tourne.
+papa|Ton sac t'attend, tout en bas.
+narrateur|En ce moment, Sarah touche le sac.
+narrateur|Le tissu est un peu rêche.
+enfant-f|Je veux jouer !
+maman|D'accord. On prépare le sac d'abord.
+papa|On met dans le sac ce que maman a dit.
+papa|Ou ce que papa a dit.
+enfant-f|J'écoute.
+maman|Oui. On met ce que l'adulte a dit.
+narrateur|L'oiseau en papier tourne encore.
+narrateur|La chaussette jaune ne bouge pas.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1353,7 +1390,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>On va où, après le sac ? Le bac à sable, le toboggan, ou les balançoires ? Tu choisis. Ensuite on met dans le sac.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1554,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|On va où, après le sac ?
+papa|Le bac à sable, le toboggan, ou les balançoires ?
+maman|Tu choisis.
+maman|Ensuite on met dans le sac.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1585,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Zoé va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Zoé se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tait une seconde. Je suis là. On reste ensemble.</t>
+          <t>Sarah s'assoit près du sac, au pied du lit. Elle pense au bac à sable. Le sable serait frais, un peu humide. Près du sac, une petite pelle jaune attend déjà. On va au bac, plus tard. D'abord le sac. On met dans le sac ce que l'adulte a dit. Le sac, papa. Sarah ouvre le sac rouge. Zzz, un peu. L'intérieur sent le tissu. Bravo. Tu as ouvert le sac. On met ce que j'ai dit. Ou ce que papa a dit. J'écoute. L'oiseau en papier tourne encore. La chaussette jaune dort sur la lampe.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,8 +1725,21 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Zoé va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Zoé se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tait une seconde.
-maman|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Sarah s'assoit près du sac, au pied du lit.
+narrateur|Elle pense au bac à sable.
+narrateur|Le sable serait frais, un peu humide.
+narrateur|Près du sac, une petite pelle jaune attend déjà.
+maman|On va au bac, plus tard.
+maman|D'abord le sac.
+papa|On met dans le sac ce que l'adulte a dit.
+enfant-f|Le sac, papa.
+narrateur|Sarah ouvre le sac rouge. Zzz, un peu.
+narrateur|L'intérieur sent le tissu.
+papa|Bravo. Tu as ouvert le sac.
+maman|On met ce que j'ai dit. Ou ce que papa a dit.
+enfant-f|J'écoute.
+narrateur|L'oiseau en papier tourne encore.
+narrateur|La chaussette jaune dort sur la lampe.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1714,7 +1767,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Préparer son sac.</t>
+          <t>Sarah prépare le sac. Elle met quoi ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1874,7 +1927,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Préparer son sac.</t>
+          <t>narrateur|Sarah prépare le sac.
+maman|Elle met quoi ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1902,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans le sac. Zoé respire. Zoé retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+          <t>Oui. On met dans le sac. Ce que l'adulte a dit. Bravo. Le sac rouge reste ouvert, tout calme. Je mets ce que tu as dit. Oui. Le sac d'abord. Un rayon passe entre deux lunes du rideau.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2046,7 +2100,13 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Zoé respire. Zoé retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+          <t>papa|Oui. On met dans le sac.
+maman|Ce que l'adulte a dit.
+maman|Bravo.
+narrateur|Le sac rouge reste ouvert, tout calme.
+enfant-f|Je mets ce que tu as dit.
+papa|Oui. Le sac d'abord.
+narrateur|Un rayon passe entre deux lunes du rideau.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2074,7 +2134,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>On glisse aussi quoi dans le sac ? Le ballon, le seau, ou le doudou ? On met ce que l'adulte a dit. Puis encore une chose.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2238,7 +2298,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|On glisse aussi quoi dans le sac ?
+papa|Le ballon, le seau, ou le doudou ?
+maman|On met ce que l'adulte a dit.
+maman|Puis encore une chose.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2266,7 +2329,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
+          <t>Sarah pense au bac à sable, dans sa chambre. Le ballon rouge attend près du sac. Le ballon est lisse, un peu frais. Le ballon, maman. D'accord. On le met dans le sac. C'est ce que l'adulte a dit. Sarah pousse le ballon. Il rentre, tout juste. Le tissu du sac se tend un peu. Bravo. Le ballon est dedans. Tu as mis ce que j'ai dit ? Oui. Dans le sac. La sangle retombe sur le ballon, molle. L'oiseau en papier tourne au-dessus.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2406,7 +2469,19 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
+          <t>narrateur|Sarah pense au bac à sable, dans sa chambre.
+narrateur|Le ballon rouge attend près du sac.
+narrateur|Le ballon est lisse, un peu frais.
+enfant-f|Le ballon, maman.
+maman|D'accord. On le met dans le sac.
+papa|C'est ce que l'adulte a dit.
+narrateur|Sarah pousse le ballon. Il rentre, tout juste.
+narrateur|Le tissu du sac se tend un peu.
+papa|Bravo. Le ballon est dedans.
+maman|Tu as mis ce que j'ai dit ?
+enfant-f|Oui. Dans le sac.
+narrateur|La sangle retombe sur le ballon, molle.
+narrateur|L'oiseau en papier tourne au-dessus.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2434,7 +2509,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On met encore quoi ? Le livre, le pull, ou la pomme ? On met dans le sac. Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2602,7 +2677,10 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On met encore quoi ?
+papa|Le livre, le pull, ou la pomme ?
+maman|On met dans le sac.
+maman|Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2630,7 +2708,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Tom. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au bac à sable, dans sa chambre. Le ballon rouge attend près du sac. Le petit livre a une couverture rouge. Les pages sentent le papier. On met le livre dans le sac. C'est ce que l'adulte a dit. Le livre, papa. Sarah prend le livre. Il est lisse, un peu froid. Elle le glisse à côté, dans le sac. Bravo. Le livre est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah appuie sur la fermeture. Zzz. Le sac rouge est fermé, un peu bosselé. Merci, Sarah. Tu as fait du bon travail. Le ballon appuie un peu sur le livre, au fond. L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2770,7 +2848,23 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Tom. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au bac à sable, dans sa chambre.
+narrateur|Le ballon rouge attend près du sac.
+narrateur|Le petit livre a une couverture rouge.
+narrateur|Les pages sentent le papier.
+papa|On met le livre dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|Le livre, papa.
+narrateur|Sarah prend le livre. Il est lisse, un peu froid.
+narrateur|Elle le glisse à côté, dans le sac.
+maman|Bravo. Le livre est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah appuie sur la fermeture. Zzz.
+narrateur|Le sac rouge est fermé, un peu bosselé.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le ballon appuie un peu sur le livre, au fond.
+narrateur|L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2798,7 +2892,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au bac à sable. Sarah a mis le ballon dans le sac. Sarah a mis le livre aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. L'oiseau en papier tourne encore, tout blanc. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2938,7 +3032,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au bac à sable.
+narrateur|Sarah a mis le ballon dans le sac.
+narrateur|Sarah a mis le livre aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|L'oiseau en papier tourne encore, tout blanc.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2966,7 +3069,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Léa. La lumière est claire. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au bac à sable, dans sa chambre. Le ballon rouge attend près du sac. Le pull à étoile attend sur la chaise. La laine est un peu rêche, un peu chaude. On met le pull dans le sac. C'est ce que l'adulte a dit. Le pull, maman. Sarah plie le pull, comme papa. L'étoile disparaît dans le sac rouge. Bravo. Le pull est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah tire la sangle. Clic. Le sac est plus lourd, tout prêt. Merci, Sarah. Tu as fait du bon travail. Le ballon se cale contre le pull à étoile. La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3106,7 +3209,23 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Léa. La lumière est claire. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au bac à sable, dans sa chambre.
+narrateur|Le ballon rouge attend près du sac.
+narrateur|Le pull à étoile attend sur la chaise.
+narrateur|La laine est un peu rêche, un peu chaude.
+maman|On met le pull dans le sac.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le pull, maman.
+narrateur|Sarah plie le pull, comme papa.
+narrateur|L'étoile disparaît dans le sac rouge.
+papa|Bravo. Le pull est dedans.
+maman|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah tire la sangle. Clic.
+narrateur|Le sac est plus lourd, tout prêt.
+papa|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le ballon se cale contre le pull à étoile.
+narrateur|La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3134,7 +3253,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au bac à sable. Sarah a mis le ballon dans le sac. Sarah a mis le pull aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. La chaise est vide. L'étoile est partie. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3274,7 +3393,16 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au bac à sable.
+narrateur|Sarah a mis le ballon dans le sac.
+narrateur|Sarah a mis le pull aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|La chaise est vide. L'étoile est partie.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3302,7 +3430,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Sami. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au bac à sable, dans sa chambre. Le ballon rouge attend près du sac. Une pomme verte brille sur la commode. Elle est froide, un peu lisse. On met la pomme dans le sac. C'est ce que l'adulte a dit. La pomme, papa. Sarah prend la pomme. Elle sent le sucre. Elle la pose tout doux, dans le sac. Bravo. La pomme est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah ferme le sac. Zzz, puis clic. La commode n'a plus sa pomme verte. Merci, Sarah. Tu as fait du bon travail. Le ballon roule vers la pomme, tout doux. Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3442,7 +3570,23 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Sami. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au bac à sable, dans sa chambre.
+narrateur|Le ballon rouge attend près du sac.
+narrateur|Une pomme verte brille sur la commode.
+narrateur|Elle est froide, un peu lisse.
+papa|On met la pomme dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|La pomme, papa.
+narrateur|Sarah prend la pomme. Elle sent le sucre.
+narrateur|Elle la pose tout doux, dans le sac.
+maman|Bravo. La pomme est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah ferme le sac. Zzz, puis clic.
+narrateur|La commode n'a plus sa pomme verte.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le ballon roule vers la pomme, tout doux.
+narrateur|Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3470,7 +3614,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au bac à sable. Sarah a mis le ballon dans le sac. Sarah a mis la pomme aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. Un rayon reste sur la commode, vide. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3610,7 +3754,16 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au bac à sable.
+narrateur|Sarah a mis le ballon dans le sac.
+narrateur|Sarah a mis la pomme aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Un rayon reste sur la commode, vide.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3638,7 +3791,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
+          <t>Sarah pense au bac à sable, dans sa chambre. Le petit seau bleu attend près du sac. L'anse du seau fait ting, tout petit. Le seau, papa. D'accord. On le met dans le sac. C'est ce que l'adulte a dit. Sarah penche le seau. Il glisse au fond. Le sac fait un petit bruit de plastique. Bravo. Le seau est dedans. Tu as mis ce que j'ai dit ? Oui. Dans le sac. L'anse dépasse un peu, puis rentre. Le pull à étoile n'a pas bougé, sur la chaise.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3778,7 +3931,19 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
+          <t>narrateur|Sarah pense au bac à sable, dans sa chambre.
+narrateur|Le petit seau bleu attend près du sac.
+narrateur|L'anse du seau fait ting, tout petit.
+enfant-f|Le seau, papa.
+papa|D'accord. On le met dans le sac.
+maman|C'est ce que l'adulte a dit.
+narrateur|Sarah penche le seau. Il glisse au fond.
+narrateur|Le sac fait un petit bruit de plastique.
+maman|Bravo. Le seau est dedans.
+papa|Tu as mis ce que j'ai dit ?
+enfant-f|Oui. Dans le sac.
+narrateur|L'anse dépasse un peu, puis rentre.
+narrateur|Le pull à étoile n'a pas bougé, sur la chaise.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3806,7 +3971,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On met encore quoi ? Le livre, le pull, ou la pomme ? On met dans le sac. Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3974,7 +4139,10 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On met encore quoi ?
+papa|Le livre, le pull, ou la pomme ?
+maman|On met dans le sac.
+maman|Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4002,7 +4170,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Tom. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au bac à sable, dans sa chambre. Le petit seau bleu attend près du sac. Le petit livre a une couverture rouge. Les pages sentent le papier. On met le livre dans le sac. C'est ce que l'adulte a dit. Le livre, papa. Sarah prend le livre. Il est lisse, un peu froid. Elle le glisse à côté, dans le sac. Bravo. Le livre est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah appuie sur la fermeture. Zzz. Le sac rouge est fermé, un peu bosselé. Merci, Sarah. Tu as fait du bon travail. Le seau bleu garde le livre au sec. L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4142,7 +4310,23 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Tom. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au bac à sable, dans sa chambre.
+narrateur|Le petit seau bleu attend près du sac.
+narrateur|Le petit livre a une couverture rouge.
+narrateur|Les pages sentent le papier.
+papa|On met le livre dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|Le livre, papa.
+narrateur|Sarah prend le livre. Il est lisse, un peu froid.
+narrateur|Elle le glisse à côté, dans le sac.
+maman|Bravo. Le livre est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah appuie sur la fermeture. Zzz.
+narrateur|Le sac rouge est fermé, un peu bosselé.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le seau bleu garde le livre au sec.
+narrateur|L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4170,7 +4354,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au bac à sable. Sarah a mis le seau dans le sac. Sarah a mis le livre aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. L'oiseau en papier tourne encore, tout blanc. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4310,7 +4494,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au bac à sable.
+narrateur|Sarah a mis le seau dans le sac.
+narrateur|Sarah a mis le livre aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|L'oiseau en papier tourne encore, tout blanc.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4338,7 +4531,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Léa. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au bac à sable, dans sa chambre. Le petit seau bleu attend près du sac. Le pull à étoile attend sur la chaise. La laine est un peu rêche, un peu chaude. On met le pull dans le sac. C'est ce que l'adulte a dit. Le pull, maman. Sarah plie le pull, comme papa. L'étoile disparaît dans le sac rouge. Bravo. Le pull est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah tire la sangle. Clic. Le sac est plus lourd, tout prêt. Merci, Sarah. Tu as fait du bon travail. Le seau s'enfonce dans le pull plié. La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4478,7 +4671,23 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Léa. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au bac à sable, dans sa chambre.
+narrateur|Le petit seau bleu attend près du sac.
+narrateur|Le pull à étoile attend sur la chaise.
+narrateur|La laine est un peu rêche, un peu chaude.
+maman|On met le pull dans le sac.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le pull, maman.
+narrateur|Sarah plie le pull, comme papa.
+narrateur|L'étoile disparaît dans le sac rouge.
+papa|Bravo. Le pull est dedans.
+maman|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah tire la sangle. Clic.
+narrateur|Le sac est plus lourd, tout prêt.
+papa|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le seau s'enfonce dans le pull plié.
+narrateur|La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4506,7 +4715,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au bac à sable. Sarah a mis le seau dans le sac. Sarah a mis le pull aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. La chaise est vide. L'étoile est partie. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4646,7 +4855,16 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au bac à sable.
+narrateur|Sarah a mis le seau dans le sac.
+narrateur|Sarah a mis le pull aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|La chaise est vide. L'étoile est partie.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4674,7 +4892,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Sami. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au bac à sable, dans sa chambre. Le petit seau bleu attend près du sac. Une pomme verte brille sur la commode. Elle est froide, un peu lisse. On met la pomme dans le sac. C'est ce que l'adulte a dit. La pomme, papa. Sarah prend la pomme. Elle sent le sucre. Elle la pose tout doux, dans le sac. Bravo. La pomme est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah ferme le sac. Zzz, puis clic. La commode n'a plus sa pomme verte. Merci, Sarah. Tu as fait du bon travail. La pomme sonne un peu contre le seau. Ting. Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4814,7 +5032,23 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Sami. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au bac à sable, dans sa chambre.
+narrateur|Le petit seau bleu attend près du sac.
+narrateur|Une pomme verte brille sur la commode.
+narrateur|Elle est froide, un peu lisse.
+papa|On met la pomme dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|La pomme, papa.
+narrateur|Sarah prend la pomme. Elle sent le sucre.
+narrateur|Elle la pose tout doux, dans le sac.
+maman|Bravo. La pomme est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah ferme le sac. Zzz, puis clic.
+narrateur|La commode n'a plus sa pomme verte.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|La pomme sonne un peu contre le seau. Ting.
+narrateur|Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4842,7 +5076,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au bac à sable. Sarah a mis le seau dans le sac. Sarah a mis la pomme aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. Un rayon reste sur la commode, vide. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4982,7 +5216,16 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au bac à sable.
+narrateur|Sarah a mis le seau dans le sac.
+narrateur|Sarah a mis la pomme aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Un rayon reste sur la commode, vide.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5010,7 +5253,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Sarah pense au bac à sable, dans sa chambre. Le doudou beige attend sur l'oreiller. Le doudou sent le lit, encore chaud. Le doudou, maman. D'accord. On le met dans le sac. C'est ce que l'adulte a dit. Sarah glisse le doudou. Le tissu frotte, tout doux. Une oreille dépasse, puis rentre. Bravo. Le doudou est dedans. Tu as mis ce que j'ai dit ? Oui. Dans le sac. Le sac devient un peu plus lourd, un peu plus doux. La chaussette jaune ne dit rien, sur la lampe.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5150,7 +5393,19 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>narrateur|Sarah pense au bac à sable, dans sa chambre.
+narrateur|Le doudou beige attend sur l'oreiller.
+narrateur|Le doudou sent le lit, encore chaud.
+enfant-f|Le doudou, maman.
+maman|D'accord. On le met dans le sac.
+papa|C'est ce que l'adulte a dit.
+narrateur|Sarah glisse le doudou. Le tissu frotte, tout doux.
+narrateur|Une oreille dépasse, puis rentre.
+papa|Bravo. Le doudou est dedans.
+maman|Tu as mis ce que j'ai dit ?
+enfant-f|Oui. Dans le sac.
+narrateur|Le sac devient un peu plus lourd, un peu plus doux.
+narrateur|La chaussette jaune ne dit rien, sur la lampe.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5178,7 +5433,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On met encore quoi ? Le livre, le pull, ou la pomme ? On met dans le sac. Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5346,7 +5601,10 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On met encore quoi ?
+papa|Le livre, le pull, ou la pomme ?
+maman|On met dans le sac.
+maman|Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5374,7 +5632,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Tom. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au bac à sable, dans sa chambre. Le doudou beige attend sur l'oreiller. Le petit livre a une couverture rouge. Les pages sentent le papier. On met le livre dans le sac. C'est ce que l'adulte a dit. Le livre, papa. Sarah prend le livre. Il est lisse, un peu froid. Elle le glisse à côté, dans le sac. Bravo. Le livre est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah appuie sur la fermeture. Zzz. Le sac rouge est fermé, un peu bosselé. Merci, Sarah. Tu as fait du bon travail. Le doudou s'adosse au livre, tout calme. L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5514,7 +5772,23 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Tom. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au bac à sable, dans sa chambre.
+narrateur|Le doudou beige attend sur l'oreiller.
+narrateur|Le petit livre a une couverture rouge.
+narrateur|Les pages sentent le papier.
+papa|On met le livre dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|Le livre, papa.
+narrateur|Sarah prend le livre. Il est lisse, un peu froid.
+narrateur|Elle le glisse à côté, dans le sac.
+maman|Bravo. Le livre est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah appuie sur la fermeture. Zzz.
+narrateur|Le sac rouge est fermé, un peu bosselé.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le doudou s'adosse au livre, tout calme.
+narrateur|L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5542,7 +5816,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au bac à sable. Sarah a mis le doudou dans le sac. Sarah a mis le livre aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. L'oiseau en papier tourne encore, tout blanc. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5682,7 +5956,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au bac à sable.
+narrateur|Sarah a mis le doudou dans le sac.
+narrateur|Sarah a mis le livre aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|L'oiseau en papier tourne encore, tout blanc.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5710,7 +5993,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Léa. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au bac à sable, dans sa chambre. Le doudou beige attend sur l'oreiller. Le pull à étoile attend sur la chaise. La laine est un peu rêche, un peu chaude. On met le pull dans le sac. C'est ce que l'adulte a dit. Le pull, maman. Sarah plie le pull, comme papa. L'étoile disparaît dans le sac rouge. Bravo. Le pull est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah tire la sangle. Clic. Le sac est plus lourd, tout prêt. Merci, Sarah. Tu as fait du bon travail. Le doudou se cache dans le pull à étoile. La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5850,7 +6133,23 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Léa. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au bac à sable, dans sa chambre.
+narrateur|Le doudou beige attend sur l'oreiller.
+narrateur|Le pull à étoile attend sur la chaise.
+narrateur|La laine est un peu rêche, un peu chaude.
+maman|On met le pull dans le sac.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le pull, maman.
+narrateur|Sarah plie le pull, comme papa.
+narrateur|L'étoile disparaît dans le sac rouge.
+papa|Bravo. Le pull est dedans.
+maman|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah tire la sangle. Clic.
+narrateur|Le sac est plus lourd, tout prêt.
+papa|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le doudou se cache dans le pull à étoile.
+narrateur|La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5878,7 +6177,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au bac à sable. Sarah a mis le doudou dans le sac. Sarah a mis le pull aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. La chaise est vide. L'étoile est partie. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6018,7 +6317,16 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au bac à sable.
+narrateur|Sarah a mis le doudou dans le sac.
+narrateur|Sarah a mis le pull aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|La chaise est vide. L'étoile est partie.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6046,7 +6354,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Sami. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au bac à sable, dans sa chambre. Le doudou beige attend sur l'oreiller. Une pomme verte brille sur la commode. Elle est froide, un peu lisse. On met la pomme dans le sac. C'est ce que l'adulte a dit. La pomme, papa. Sarah prend la pomme. Elle sent le sucre. Elle la pose tout doux, dans le sac. Bravo. La pomme est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah ferme le sac. Zzz, puis clic. La commode n'a plus sa pomme verte. Merci, Sarah. Tu as fait du bon travail. Le doudou veille près de la pomme verte. Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6186,7 +6494,23 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Sami. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au bac à sable, dans sa chambre.
+narrateur|Le doudou beige attend sur l'oreiller.
+narrateur|Une pomme verte brille sur la commode.
+narrateur|Elle est froide, un peu lisse.
+papa|On met la pomme dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|La pomme, papa.
+narrateur|Sarah prend la pomme. Elle sent le sucre.
+narrateur|Elle la pose tout doux, dans le sac.
+maman|Bravo. La pomme est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah ferme le sac. Zzz, puis clic.
+narrateur|La commode n'a plus sa pomme verte.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le doudou veille près de la pomme verte.
+narrateur|Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6214,7 +6538,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au bac à sable. Sarah a mis le doudou dans le sac. Sarah a mis la pomme aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. Un rayon reste sur la commode, vide. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6354,7 +6678,16 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au bac à sable.
+narrateur|Sarah a mis le doudou dans le sac.
+narrateur|Sarah a mis la pomme aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Un rayon reste sur la commode, vide.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6382,7 +6715,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Zoé va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Zoé se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tient la main. Je suis là. On reste ensemble.</t>
+          <t>Sarah s'assoit sur le tapis, près du sac. Elle pense au toboggan jaune. La rampe serait lisse, un peu froide. Un cube jaune, comme le toboggan, est sous le lit. On verra le toboggan, plus tard. D'abord le sac. On met dans le sac ce que l'adulte a dit. Le sac, maman. Sarah tire la sangle. Elle est un peu rêche. Le sac s'ouvre comme une bouche rouge. Bravo. Tu as ouvert le sac. On met ce que maman a dit. Ou ce que j'ai dit. J'écoute. Le pull à étoile attend sur la chaise. L'oiseau en papier fait un tour, tout lent.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6522,8 +6855,21 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Zoé va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Zoé se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On se tient la main.
-maman|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Sarah s'assoit sur le tapis, près du sac.
+narrateur|Elle pense au toboggan jaune.
+narrateur|La rampe serait lisse, un peu froide.
+narrateur|Un cube jaune, comme le toboggan, est sous le lit.
+papa|On verra le toboggan, plus tard.
+papa|D'abord le sac.
+maman|On met dans le sac ce que l'adulte a dit.
+enfant-f|Le sac, maman.
+narrateur|Sarah tire la sangle. Elle est un peu rêche.
+narrateur|Le sac s'ouvre comme une bouche rouge.
+maman|Bravo. Tu as ouvert le sac.
+papa|On met ce que maman a dit. Ou ce que j'ai dit.
+enfant-f|J'écoute.
+narrateur|Le pull à étoile attend sur la chaise.
+narrateur|L'oiseau en papier fait un tour, tout lent.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6551,7 +6897,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Préparer son sac.</t>
+          <t>Sarah prépare le sac. Elle met quoi ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6711,7 +7057,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Préparer son sac.</t>
+          <t>narrateur|Sarah prépare le sac.
+papa|Elle met quoi ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6739,7 +7086,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans le sac. Zoé respire. Zoé retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+          <t>Oui. On met dans le sac. Ce que l'adulte a dit. Bravo. La sangle retombe, molle. Je mets ce que tu as dit. Oui. Le sac d'abord. La poussière danse encore dans le rayon.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6883,7 +7230,13 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Zoé respire. Zoé retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+          <t>maman|Oui. On met dans le sac.
+papa|Ce que l'adulte a dit.
+papa|Bravo.
+narrateur|La sangle retombe, molle.
+enfant-f|Je mets ce que tu as dit.
+maman|Oui. Le sac d'abord.
+narrateur|La poussière danse encore dans le rayon.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6911,7 +7264,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>On glisse aussi quoi dans le sac ? Le ballon, le seau, ou le doudou ? On met ce que l'adulte a dit. Puis encore une chose.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7075,7 +7428,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|On glisse aussi quoi dans le sac ?
+papa|Le ballon, le seau, ou le doudou ?
+maman|On met ce que l'adulte a dit.
+maman|Puis encore une chose.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7103,7 +7459,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
+          <t>Sarah pense au toboggan, dans sa chambre. Le ballon rouge attend près du sac. Le ballon est lisse, un peu frais. Le ballon, maman. D'accord. On le met dans le sac. C'est ce que l'adulte a dit. Sarah pousse le ballon. Il rentre, tout juste. Le tissu du sac se tend un peu. Bravo. Le ballon est dedans. Tu as mis ce que j'ai dit ? Oui. Dans le sac. La sangle retombe sur le ballon, molle. L'oiseau en papier tourne au-dessus.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7243,7 +7599,19 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
+          <t>narrateur|Sarah pense au toboggan, dans sa chambre.
+narrateur|Le ballon rouge attend près du sac.
+narrateur|Le ballon est lisse, un peu frais.
+enfant-f|Le ballon, maman.
+maman|D'accord. On le met dans le sac.
+papa|C'est ce que l'adulte a dit.
+narrateur|Sarah pousse le ballon. Il rentre, tout juste.
+narrateur|Le tissu du sac se tend un peu.
+papa|Bravo. Le ballon est dedans.
+maman|Tu as mis ce que j'ai dit ?
+enfant-f|Oui. Dans le sac.
+narrateur|La sangle retombe sur le ballon, molle.
+narrateur|L'oiseau en papier tourne au-dessus.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7271,7 +7639,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On met encore quoi ? Le livre, le pull, ou la pomme ? On met dans le sac. Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7439,7 +7807,10 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On met encore quoi ?
+papa|Le livre, le pull, ou la pomme ?
+maman|On met dans le sac.
+maman|Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7467,7 +7838,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Tom. La lumière est claire. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au toboggan, dans sa chambre. Le ballon rouge attend près du sac. Le petit livre a une couverture rouge. Les pages sentent le papier. On met le livre dans le sac. C'est ce que l'adulte a dit. Le livre, papa. Sarah prend le livre. Il est lisse, un peu froid. Elle le glisse à côté, dans le sac. Bravo. Le livre est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah appuie sur la fermeture. Zzz. Le sac rouge est fermé, un peu bosselé. Merci, Sarah. Tu as fait du bon travail. Le ballon et le livre font un petit bosse, ensemble. L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7607,7 +7978,23 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Tom. La lumière est claire. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au toboggan, dans sa chambre.
+narrateur|Le ballon rouge attend près du sac.
+narrateur|Le petit livre a une couverture rouge.
+narrateur|Les pages sentent le papier.
+papa|On met le livre dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|Le livre, papa.
+narrateur|Sarah prend le livre. Il est lisse, un peu froid.
+narrateur|Elle le glisse à côté, dans le sac.
+maman|Bravo. Le livre est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah appuie sur la fermeture. Zzz.
+narrateur|Le sac rouge est fermé, un peu bosselé.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le ballon et le livre font un petit bosse, ensemble.
+narrateur|L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7635,7 +8022,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au toboggan. Sarah a mis le ballon dans le sac. Sarah a mis le livre aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. L'oiseau en papier tourne encore, tout blanc. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7775,7 +8162,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au toboggan.
+narrateur|Sarah a mis le ballon dans le sac.
+narrateur|Sarah a mis le livre aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|L'oiseau en papier tourne encore, tout blanc.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7803,7 +8199,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Léa. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au toboggan, dans sa chambre. Le ballon rouge attend près du sac. Le pull à étoile attend sur la chaise. La laine est un peu rêche, un peu chaude. On met le pull dans le sac. C'est ce que l'adulte a dit. Le pull, maman. Sarah plie le pull, comme papa. L'étoile disparaît dans le sac rouge. Bravo. Le pull est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah tire la sangle. Clic. Le sac est plus lourd, tout prêt. Merci, Sarah. Tu as fait du bon travail. Le ballon disparaît sous le pull. La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7943,7 +8339,23 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Léa. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au toboggan, dans sa chambre.
+narrateur|Le ballon rouge attend près du sac.
+narrateur|Le pull à étoile attend sur la chaise.
+narrateur|La laine est un peu rêche, un peu chaude.
+maman|On met le pull dans le sac.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le pull, maman.
+narrateur|Sarah plie le pull, comme papa.
+narrateur|L'étoile disparaît dans le sac rouge.
+papa|Bravo. Le pull est dedans.
+maman|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah tire la sangle. Clic.
+narrateur|Le sac est plus lourd, tout prêt.
+papa|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le ballon disparaît sous le pull.
+narrateur|La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7971,7 +8383,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au toboggan. Sarah a mis le ballon dans le sac. Sarah a mis le pull aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. La chaise est vide. L'étoile est partie. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8111,7 +8523,16 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au toboggan.
+narrateur|Sarah a mis le ballon dans le sac.
+narrateur|Sarah a mis le pull aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|La chaise est vide. L'étoile est partie.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8139,7 +8560,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Sami. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au toboggan, dans sa chambre. Le ballon rouge attend près du sac. Une pomme verte brille sur la commode. Elle est froide, un peu lisse. On met la pomme dans le sac. C'est ce que l'adulte a dit. La pomme, papa. Sarah prend la pomme. Elle sent le sucre. Elle la pose tout doux, dans le sac. Bravo. La pomme est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah ferme le sac. Zzz, puis clic. La commode n'a plus sa pomme verte. Merci, Sarah. Tu as fait du bon travail. Le ballon laisse une place ronde à la pomme. Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8279,7 +8700,23 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Sami. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au toboggan, dans sa chambre.
+narrateur|Le ballon rouge attend près du sac.
+narrateur|Une pomme verte brille sur la commode.
+narrateur|Elle est froide, un peu lisse.
+papa|On met la pomme dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|La pomme, papa.
+narrateur|Sarah prend la pomme. Elle sent le sucre.
+narrateur|Elle la pose tout doux, dans le sac.
+maman|Bravo. La pomme est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah ferme le sac. Zzz, puis clic.
+narrateur|La commode n'a plus sa pomme verte.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le ballon laisse une place ronde à la pomme.
+narrateur|Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8307,7 +8744,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au toboggan. Sarah a mis le ballon dans le sac. Sarah a mis la pomme aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. Un rayon reste sur la commode, vide. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8447,7 +8884,16 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au toboggan.
+narrateur|Sarah a mis le ballon dans le sac.
+narrateur|Sarah a mis la pomme aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Un rayon reste sur la commode, vide.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8475,7 +8921,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
+          <t>Sarah pense au toboggan, dans sa chambre. Le petit seau bleu attend près du sac. L'anse du seau fait ting, tout petit. Le seau, papa. D'accord. On le met dans le sac. C'est ce que l'adulte a dit. Sarah penche le seau. Il glisse au fond. Le sac fait un petit bruit de plastique. Bravo. Le seau est dedans. Tu as mis ce que j'ai dit ? Oui. Dans le sac. L'anse dépasse un peu, puis rentre. Le pull à étoile n'a pas bougé, sur la chaise.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8615,7 +9061,19 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
+          <t>narrateur|Sarah pense au toboggan, dans sa chambre.
+narrateur|Le petit seau bleu attend près du sac.
+narrateur|L'anse du seau fait ting, tout petit.
+enfant-f|Le seau, papa.
+papa|D'accord. On le met dans le sac.
+maman|C'est ce que l'adulte a dit.
+narrateur|Sarah penche le seau. Il glisse au fond.
+narrateur|Le sac fait un petit bruit de plastique.
+maman|Bravo. Le seau est dedans.
+papa|Tu as mis ce que j'ai dit ?
+enfant-f|Oui. Dans le sac.
+narrateur|L'anse dépasse un peu, puis rentre.
+narrateur|Le pull à étoile n'a pas bougé, sur la chaise.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8643,7 +9101,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On met encore quoi ? Le livre, le pull, ou la pomme ? On met dans le sac. Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8811,7 +9269,10 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On met encore quoi ?
+papa|Le livre, le pull, ou la pomme ?
+maman|On met dans le sac.
+maman|Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8839,7 +9300,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Tom. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au toboggan, dans sa chambre. Le petit seau bleu attend près du sac. Le petit livre a une couverture rouge. Les pages sentent le papier. On met le livre dans le sac. C'est ce que l'adulte a dit. Le livre, papa. Sarah prend le livre. Il est lisse, un peu froid. Elle le glisse à côté, dans le sac. Bravo. Le livre est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah appuie sur la fermeture. Zzz. Le sac rouge est fermé, un peu bosselé. Merci, Sarah. Tu as fait du bon travail. Le seau et le livre tiennent dans un coin du sac. L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8979,7 +9440,23 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Tom. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au toboggan, dans sa chambre.
+narrateur|Le petit seau bleu attend près du sac.
+narrateur|Le petit livre a une couverture rouge.
+narrateur|Les pages sentent le papier.
+papa|On met le livre dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|Le livre, papa.
+narrateur|Sarah prend le livre. Il est lisse, un peu froid.
+narrateur|Elle le glisse à côté, dans le sac.
+maman|Bravo. Le livre est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah appuie sur la fermeture. Zzz.
+narrateur|Le sac rouge est fermé, un peu bosselé.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le seau et le livre tiennent dans un coin du sac.
+narrateur|L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9007,7 +9484,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au toboggan. Sarah a mis le seau dans le sac. Sarah a mis le livre aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. L'oiseau en papier tourne encore, tout blanc. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9147,7 +9624,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au toboggan.
+narrateur|Sarah a mis le seau dans le sac.
+narrateur|Sarah a mis le livre aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|L'oiseau en papier tourne encore, tout blanc.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9175,7 +9661,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Léa. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le toboggan, le seau et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au toboggan, dans sa chambre. Le petit seau bleu attend près du sac. Le pull à étoile attend sur la chaise. La laine est un peu rêche, un peu chaude. On met le pull dans le sac. C'est ce que l'adulte a dit. Le pull, maman. Sarah plie le pull, comme papa. L'étoile disparaît dans le sac rouge. Bravo. Le pull est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah tire la sangle. Clic. Le sac est plus lourd, tout prêt. Merci, Sarah. Tu as fait du bon travail. Le pull enveloppe le seau, tout chaud. La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9315,7 +9801,23 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Léa. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le toboggan, le seau et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au toboggan, dans sa chambre.
+narrateur|Le petit seau bleu attend près du sac.
+narrateur|Le pull à étoile attend sur la chaise.
+narrateur|La laine est un peu rêche, un peu chaude.
+maman|On met le pull dans le sac.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le pull, maman.
+narrateur|Sarah plie le pull, comme papa.
+narrateur|L'étoile disparaît dans le sac rouge.
+papa|Bravo. Le pull est dedans.
+maman|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah tire la sangle. Clic.
+narrateur|Le sac est plus lourd, tout prêt.
+papa|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le pull enveloppe le seau, tout chaud.
+narrateur|La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9343,7 +9845,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au toboggan. Sarah a mis le seau dans le sac. Sarah a mis le pull aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. La chaise est vide. L'étoile est partie. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9483,7 +9985,16 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au toboggan.
+narrateur|Sarah a mis le seau dans le sac.
+narrateur|Sarah a mis le pull aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|La chaise est vide. L'étoile est partie.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9511,7 +10022,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Sami. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au toboggan, dans sa chambre. Le petit seau bleu attend près du sac. Une pomme verte brille sur la commode. Elle est froide, un peu lisse. On met la pomme dans le sac. C'est ce que l'adulte a dit. La pomme, papa. Sarah prend la pomme. Elle sent le sucre. Elle la pose tout doux, dans le sac. Bravo. La pomme est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah ferme le sac. Zzz, puis clic. La commode n'a plus sa pomme verte. Merci, Sarah. Tu as fait du bon travail. La pomme se loge près de l'anse, au fond. Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9651,7 +10162,23 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Sami. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au toboggan, dans sa chambre.
+narrateur|Le petit seau bleu attend près du sac.
+narrateur|Une pomme verte brille sur la commode.
+narrateur|Elle est froide, un peu lisse.
+papa|On met la pomme dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|La pomme, papa.
+narrateur|Sarah prend la pomme. Elle sent le sucre.
+narrateur|Elle la pose tout doux, dans le sac.
+maman|Bravo. La pomme est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah ferme le sac. Zzz, puis clic.
+narrateur|La commode n'a plus sa pomme verte.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|La pomme se loge près de l'anse, au fond.
+narrateur|Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9679,7 +10206,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au toboggan. Sarah a mis le seau dans le sac. Sarah a mis la pomme aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. Un rayon reste sur la commode, vide. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9819,7 +10346,16 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au toboggan.
+narrateur|Sarah a mis le seau dans le sac.
+narrateur|Sarah a mis la pomme aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Un rayon reste sur la commode, vide.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9847,7 +10383,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Sarah pense au toboggan, dans sa chambre. Le doudou beige attend sur l'oreiller. Le doudou sent le lit, encore chaud. Le doudou, maman. D'accord. On le met dans le sac. C'est ce que l'adulte a dit. Sarah glisse le doudou. Le tissu frotte, tout doux. Une oreille dépasse, puis rentre. Bravo. Le doudou est dedans. Tu as mis ce que j'ai dit ? Oui. Dans le sac. Le sac devient un peu plus lourd, un peu plus doux. La chaussette jaune ne dit rien, sur la lampe.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9987,7 +10523,19 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>narrateur|Sarah pense au toboggan, dans sa chambre.
+narrateur|Le doudou beige attend sur l'oreiller.
+narrateur|Le doudou sent le lit, encore chaud.
+enfant-f|Le doudou, maman.
+maman|D'accord. On le met dans le sac.
+papa|C'est ce que l'adulte a dit.
+narrateur|Sarah glisse le doudou. Le tissu frotte, tout doux.
+narrateur|Une oreille dépasse, puis rentre.
+papa|Bravo. Le doudou est dedans.
+maman|Tu as mis ce que j'ai dit ?
+enfant-f|Oui. Dans le sac.
+narrateur|Le sac devient un peu plus lourd, un peu plus doux.
+narrateur|La chaussette jaune ne dit rien, sur la lampe.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10015,7 +10563,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On met encore quoi ? Le livre, le pull, ou la pomme ? On met dans le sac. Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10183,7 +10731,10 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On met encore quoi ?
+papa|Le livre, le pull, ou la pomme ?
+maman|On met dans le sac.
+maman|Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10211,7 +10762,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Tom. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au toboggan, dans sa chambre. Le doudou beige attend sur l'oreiller. Le petit livre a une couverture rouge. Les pages sentent le papier. On met le livre dans le sac. C'est ce que l'adulte a dit. Le livre, papa. Sarah prend le livre. Il est lisse, un peu froid. Elle le glisse à côté, dans le sac. Bravo. Le livre est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah appuie sur la fermeture. Zzz. Le sac rouge est fermé, un peu bosselé. Merci, Sarah. Tu as fait du bon travail. Le doudou pose une oreille sur le livre. L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10351,7 +10902,23 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Tom. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au toboggan, dans sa chambre.
+narrateur|Le doudou beige attend sur l'oreiller.
+narrateur|Le petit livre a une couverture rouge.
+narrateur|Les pages sentent le papier.
+papa|On met le livre dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|Le livre, papa.
+narrateur|Sarah prend le livre. Il est lisse, un peu froid.
+narrateur|Elle le glisse à côté, dans le sac.
+maman|Bravo. Le livre est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah appuie sur la fermeture. Zzz.
+narrateur|Le sac rouge est fermé, un peu bosselé.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le doudou pose une oreille sur le livre.
+narrateur|L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10379,7 +10946,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au toboggan. Sarah a mis le doudou dans le sac. Sarah a mis le livre aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. L'oiseau en papier tourne encore, tout blanc. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10519,7 +11086,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au toboggan.
+narrateur|Sarah a mis le doudou dans le sac.
+narrateur|Sarah a mis le livre aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|L'oiseau en papier tourne encore, tout blanc.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10547,7 +11123,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Léa. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au toboggan, dans sa chambre. Le doudou beige attend sur l'oreiller. Le pull à étoile attend sur la chaise. La laine est un peu rêche, un peu chaude. On met le pull dans le sac. C'est ce que l'adulte a dit. Le pull, maman. Sarah plie le pull, comme papa. L'étoile disparaît dans le sac rouge. Bravo. Le pull est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah tire la sangle. Clic. Le sac est plus lourd, tout prêt. Merci, Sarah. Tu as fait du bon travail. Le doudou et le pull se tiennent, tout doux. La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10687,7 +11263,23 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Léa. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au toboggan, dans sa chambre.
+narrateur|Le doudou beige attend sur l'oreiller.
+narrateur|Le pull à étoile attend sur la chaise.
+narrateur|La laine est un peu rêche, un peu chaude.
+maman|On met le pull dans le sac.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le pull, maman.
+narrateur|Sarah plie le pull, comme papa.
+narrateur|L'étoile disparaît dans le sac rouge.
+papa|Bravo. Le pull est dedans.
+maman|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah tire la sangle. Clic.
+narrateur|Le sac est plus lourd, tout prêt.
+papa|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le doudou et le pull se tiennent, tout doux.
+narrateur|La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10715,7 +11307,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au toboggan. Sarah a mis le doudou dans le sac. Sarah a mis le pull aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. La chaise est vide. L'étoile est partie. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10855,7 +11447,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au toboggan.
+narrateur|Sarah a mis le doudou dans le sac.
+narrateur|Sarah a mis le pull aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|La chaise est vide. L'étoile est partie.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10883,7 +11484,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Sami. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense au toboggan, dans sa chambre. Le doudou beige attend sur l'oreiller. Une pomme verte brille sur la commode. Elle est froide, un peu lisse. On met la pomme dans le sac. C'est ce que l'adulte a dit. La pomme, papa. Sarah prend la pomme. Elle sent le sucre. Elle la pose tout doux, dans le sac. Bravo. La pomme est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah ferme le sac. Zzz, puis clic. La commode n'a plus sa pomme verte. Merci, Sarah. Tu as fait du bon travail. Le doudou aime la pomme froide, tout contre. Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11023,7 +11624,23 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Sami. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense au toboggan, dans sa chambre.
+narrateur|Le doudou beige attend sur l'oreiller.
+narrateur|Une pomme verte brille sur la commode.
+narrateur|Elle est froide, un peu lisse.
+papa|On met la pomme dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|La pomme, papa.
+narrateur|Sarah prend la pomme. Elle sent le sucre.
+narrateur|Elle la pose tout doux, dans le sac.
+maman|Bravo. La pomme est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah ferme le sac. Zzz, puis clic.
+narrateur|La commode n'a plus sa pomme verte.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le doudou aime la pomme froide, tout contre.
+narrateur|Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11051,7 +11668,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé au toboggan. Sarah a mis le doudou dans le sac. Sarah a mis la pomme aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. Un rayon reste sur la commode, vide. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11191,7 +11808,16 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé au toboggan.
+narrateur|Sarah a mis le doudou dans le sac.
+narrateur|Sarah a mis la pomme aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Un rayon reste sur la commode, vide.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11219,7 +11845,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Zoé va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Zoé se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On range un objet. Je suis là. On reste ensemble.</t>
+          <t>Sarah s'agenouille près de la fenêtre. Le sac rouge est contre son genou. Elle pense aux balançoires. Les chaînes feraient cling, tout léger. Les balançoires, après. D'abord le sac. On met dans le sac ce que l'adulte a dit. Le sac, papa. Sarah glisse la main dans le sac. Le fond est vide, un peu frais. Bravo. Tu as ouvert le sac. On met ce que papa a dit. Ou ce que j'ai dit. J'écoute. Une lune bleue du rideau bouge un peu. Dehors, un vrai oiseau fait un petit cri.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11359,8 +11985,21 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Zoé va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Zoé se souvient : sac, ce que l'adulte a dit. Voici le geste : mettre dans le sac. On range un objet.
-maman|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Sarah s'agenouille près de la fenêtre.
+narrateur|Le sac rouge est contre son genou.
+narrateur|Elle pense aux balançoires.
+narrateur|Les chaînes feraient cling, tout léger.
+maman|Les balançoires, après.
+maman|D'abord le sac.
+papa|On met dans le sac ce que l'adulte a dit.
+enfant-f|Le sac, papa.
+narrateur|Sarah glisse la main dans le sac.
+narrateur|Le fond est vide, un peu frais.
+papa|Bravo. Tu as ouvert le sac.
+maman|On met ce que papa a dit. Ou ce que j'ai dit.
+enfant-f|J'écoute.
+narrateur|Une lune bleue du rideau bouge un peu.
+narrateur|Dehors, un vrai oiseau fait un petit cri.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11388,7 +12027,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Préparer son sac.</t>
+          <t>Sarah prépare le sac. Elle met quoi ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11548,7 +12187,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Préparer son sac.</t>
+          <t>narrateur|Sarah prépare le sac.
+maman|Elle met quoi ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11576,7 +12216,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : mettre dans le sac. Zoé respire. Zoé retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+          <t>Oui. On met dans le sac. Ce que l'adulte a dit. Bravo. Le genou de Sarah touche encore le sac. Je mets ce que tu as dit. Oui. Le sac d'abord. Dehors, l'oiseau se tait.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11720,7 +12360,13 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : mettre dans le sac. Zoé respire. Zoé retient : sac, ce que l'adulte a dit. On continue, avec maman.</t>
+          <t>papa|Oui. On met dans le sac.
+maman|Ce que l'adulte a dit.
+maman|Bravo.
+narrateur|Le genou de Sarah touche encore le sac.
+enfant-f|Je mets ce que tu as dit.
+papa|Oui. Le sac d'abord.
+narrateur|Dehors, l'oiseau se tait.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11748,7 +12394,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>On glisse aussi quoi dans le sac ? Le ballon, le seau, ou le doudou ? On met ce que l'adulte a dit. Puis encore une chose.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11912,7 +12558,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|On glisse aussi quoi dans le sac ?
+papa|Le ballon, le seau, ou le doudou ?
+maman|On met ce que l'adulte a dit.
+maman|Puis encore une chose.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11940,7 +12589,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
+          <t>Sarah pense aux balançoires, dans sa chambre. Le ballon rouge attend près du sac. Le ballon est lisse, un peu frais. Le ballon, maman. D'accord. On le met dans le sac. C'est ce que l'adulte a dit. Sarah pousse le ballon. Il rentre, tout juste. Le tissu du sac se tend un peu. Bravo. Le ballon est dedans. Tu as mis ce que j'ai dit ? Oui. Dans le sac. La sangle retombe sur le ballon, molle. L'oiseau en papier tourne au-dessus.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12080,7 +12729,19 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On dit merci. papa n'est pas loin.</t>
+          <t>narrateur|Sarah pense aux balançoires, dans sa chambre.
+narrateur|Le ballon rouge attend près du sac.
+narrateur|Le ballon est lisse, un peu frais.
+enfant-f|Le ballon, maman.
+maman|D'accord. On le met dans le sac.
+papa|C'est ce que l'adulte a dit.
+narrateur|Sarah pousse le ballon. Il rentre, tout juste.
+narrateur|Le tissu du sac se tend un peu.
+papa|Bravo. Le ballon est dedans.
+maman|Tu as mis ce que j'ai dit ?
+enfant-f|Oui. Dans le sac.
+narrateur|La sangle retombe sur le ballon, molle.
+narrateur|L'oiseau en papier tourne au-dessus.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12108,7 +12769,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On met encore quoi ? Le livre, le pull, ou la pomme ? On met dans le sac. Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12276,7 +12937,10 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On met encore quoi ?
+papa|Le livre, le pull, ou la pomme ?
+maman|On met dans le sac.
+maman|Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12304,7 +12968,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense aux balançoires, dans sa chambre. Le ballon rouge attend près du sac. Le petit livre a une couverture rouge. Les pages sentent le papier. On met le livre dans le sac. C'est ce que l'adulte a dit. Le livre, papa. Sarah prend le livre. Il est lisse, un peu froid. Elle le glisse à côté, dans le sac. Bravo. Le livre est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah appuie sur la fermeture. Zzz. Le sac rouge est fermé, un peu bosselé. Merci, Sarah. Tu as fait du bon travail. Près de la fenêtre, le livre glisse contre le ballon. L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12444,7 +13108,23 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense aux balançoires, dans sa chambre.
+narrateur|Le ballon rouge attend près du sac.
+narrateur|Le petit livre a une couverture rouge.
+narrateur|Les pages sentent le papier.
+papa|On met le livre dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|Le livre, papa.
+narrateur|Sarah prend le livre. Il est lisse, un peu froid.
+narrateur|Elle le glisse à côté, dans le sac.
+maman|Bravo. Le livre est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah appuie sur la fermeture. Zzz.
+narrateur|Le sac rouge est fermé, un peu bosselé.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Près de la fenêtre, le livre glisse contre le ballon.
+narrateur|L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12472,7 +13152,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé aux balançoires. Sarah a mis le ballon dans le sac. Sarah a mis le livre aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. L'oiseau en papier tourne encore, tout blanc. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12612,7 +13292,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé aux balançoires.
+narrateur|Sarah a mis le ballon dans le sac.
+narrateur|Sarah a mis le livre aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|L'oiseau en papier tourne encore, tout blanc.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12640,7 +13329,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense aux balançoires, dans sa chambre. Le ballon rouge attend près du sac. Le pull à étoile attend sur la chaise. La laine est un peu rêche, un peu chaude. On met le pull dans le sac. C'est ce que l'adulte a dit. Le pull, maman. Sarah plie le pull, comme papa. L'étoile disparaît dans le sac rouge. Bravo. Le pull est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah tire la sangle. Clic. Le sac est plus lourd, tout prêt. Merci, Sarah. Tu as fait du bon travail. Le pull sent encore la chaise, dans le sac. La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12780,7 +13469,23 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense aux balançoires, dans sa chambre.
+narrateur|Le ballon rouge attend près du sac.
+narrateur|Le pull à étoile attend sur la chaise.
+narrateur|La laine est un peu rêche, un peu chaude.
+maman|On met le pull dans le sac.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le pull, maman.
+narrateur|Sarah plie le pull, comme papa.
+narrateur|L'étoile disparaît dans le sac rouge.
+papa|Bravo. Le pull est dedans.
+maman|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah tire la sangle. Clic.
+narrateur|Le sac est plus lourd, tout prêt.
+papa|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le pull sent encore la chaise, dans le sac.
+narrateur|La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12808,7 +13513,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé aux balançoires. Sarah a mis le ballon dans le sac. Sarah a mis le pull aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. La chaise est vide. L'étoile est partie. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12948,7 +13653,16 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé aux balançoires.
+narrateur|Sarah a mis le ballon dans le sac.
+narrateur|Sarah a mis le pull aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|La chaise est vide. L'étoile est partie.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12976,7 +13690,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense aux balançoires, dans sa chambre. Le ballon rouge attend près du sac. Une pomme verte brille sur la commode. Elle est froide, un peu lisse. On met la pomme dans le sac. C'est ce que l'adulte a dit. La pomme, papa. Sarah prend la pomme. Elle sent le sucre. Elle la pose tout doux, dans le sac. Bravo. La pomme est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah ferme le sac. Zzz, puis clic. La commode n'a plus sa pomme verte. Merci, Sarah. Tu as fait du bon travail. La pomme brille un peu, même dans le sac. Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13116,7 +13830,23 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense aux balançoires, dans sa chambre.
+narrateur|Le ballon rouge attend près du sac.
+narrateur|Une pomme verte brille sur la commode.
+narrateur|Elle est froide, un peu lisse.
+papa|On met la pomme dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|La pomme, papa.
+narrateur|Sarah prend la pomme. Elle sent le sucre.
+narrateur|Elle la pose tout doux, dans le sac.
+maman|Bravo. La pomme est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah ferme le sac. Zzz, puis clic.
+narrateur|La commode n'a plus sa pomme verte.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|La pomme brille un peu, même dans le sac.
+narrateur|Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13144,7 +13874,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé aux balançoires. Sarah a mis le ballon dans le sac. Sarah a mis la pomme aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. Un rayon reste sur la commode, vide. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13284,7 +14014,16 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé aux balançoires.
+narrateur|Sarah a mis le ballon dans le sac.
+narrateur|Sarah a mis la pomme aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Un rayon reste sur la commode, vide.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13312,7 +14051,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
+          <t>Sarah pense aux balançoires, dans sa chambre. Le petit seau bleu attend près du sac. L'anse du seau fait ting, tout petit. Le seau, papa. D'accord. On le met dans le sac. C'est ce que l'adulte a dit. Sarah penche le seau. Il glisse au fond. Le sac fait un petit bruit de plastique. Bravo. Le seau est dedans. Tu as mis ce que j'ai dit ? Oui. Dans le sac. L'anse dépasse un peu, puis rentre. Le pull à étoile n'a pas bougé, sur la chaise.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13452,7 +14191,19 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On souffle doucement. papa n'est pas loin.</t>
+          <t>narrateur|Sarah pense aux balançoires, dans sa chambre.
+narrateur|Le petit seau bleu attend près du sac.
+narrateur|L'anse du seau fait ting, tout petit.
+enfant-f|Le seau, papa.
+papa|D'accord. On le met dans le sac.
+maman|C'est ce que l'adulte a dit.
+narrateur|Sarah penche le seau. Il glisse au fond.
+narrateur|Le sac fait un petit bruit de plastique.
+maman|Bravo. Le seau est dedans.
+papa|Tu as mis ce que j'ai dit ?
+enfant-f|Oui. Dans le sac.
+narrateur|L'anse dépasse un peu, puis rentre.
+narrateur|Le pull à étoile n'a pas bougé, sur la chaise.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13480,7 +14231,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On met encore quoi ? Le livre, le pull, ou la pomme ? On met dans le sac. Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13648,7 +14399,10 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On met encore quoi ?
+papa|Le livre, le pull, ou la pomme ?
+maman|On met dans le sac.
+maman|Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13676,7 +14430,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de les balançoires, le seau et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense aux balançoires, dans sa chambre. Le petit seau bleu attend près du sac. Le petit livre a une couverture rouge. Les pages sentent le papier. On met le livre dans le sac. C'est ce que l'adulte a dit. Le livre, papa. Sarah prend le livre. Il est lisse, un peu froid. Elle le glisse à côté, dans le sac. Bravo. Le livre est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah appuie sur la fermeture. Zzz. Le sac rouge est fermé, un peu bosselé. Merci, Sarah. Tu as fait du bon travail. Le seau penche. Le livre le calme. L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13816,7 +14570,23 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de les balançoires, le seau et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense aux balançoires, dans sa chambre.
+narrateur|Le petit seau bleu attend près du sac.
+narrateur|Le petit livre a une couverture rouge.
+narrateur|Les pages sentent le papier.
+papa|On met le livre dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|Le livre, papa.
+narrateur|Sarah prend le livre. Il est lisse, un peu froid.
+narrateur|Elle le glisse à côté, dans le sac.
+maman|Bravo. Le livre est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah appuie sur la fermeture. Zzz.
+narrateur|Le sac rouge est fermé, un peu bosselé.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le seau penche. Le livre le calme.
+narrateur|L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13844,7 +14614,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé aux balançoires. Sarah a mis le seau dans le sac. Sarah a mis le livre aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. L'oiseau en papier tourne encore, tout blanc. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13984,7 +14754,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé aux balançoires.
+narrateur|Sarah a mis le seau dans le sac.
+narrateur|Sarah a mis le livre aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|L'oiseau en papier tourne encore, tout blanc.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14012,7 +14791,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de les balançoires, le seau et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense aux balançoires, dans sa chambre. Le petit seau bleu attend près du sac. Le pull à étoile attend sur la chaise. La laine est un peu rêche, un peu chaude. On met le pull dans le sac. C'est ce que l'adulte a dit. Le pull, maman. Sarah plie le pull, comme papa. L'étoile disparaît dans le sac rouge. Bravo. Le pull est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah tire la sangle. Clic. Le sac est plus lourd, tout prêt. Merci, Sarah. Tu as fait du bon travail. Le pull bleu tient le seau, sans bruit. La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14152,7 +14931,23 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de les balançoires, le seau et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense aux balançoires, dans sa chambre.
+narrateur|Le petit seau bleu attend près du sac.
+narrateur|Le pull à étoile attend sur la chaise.
+narrateur|La laine est un peu rêche, un peu chaude.
+maman|On met le pull dans le sac.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le pull, maman.
+narrateur|Sarah plie le pull, comme papa.
+narrateur|L'étoile disparaît dans le sac rouge.
+papa|Bravo. Le pull est dedans.
+maman|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah tire la sangle. Clic.
+narrateur|Le sac est plus lourd, tout prêt.
+papa|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le pull bleu tient le seau, sans bruit.
+narrateur|La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14180,7 +14975,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé aux balançoires. Sarah a mis le seau dans le sac. Sarah a mis le pull aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. La chaise est vide. L'étoile est partie. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14320,7 +15115,16 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé aux balançoires.
+narrateur|Sarah a mis le seau dans le sac.
+narrateur|Sarah a mis le pull aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|La chaise est vide. L'étoile est partie.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14348,7 +15152,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense aux balançoires, dans sa chambre. Le petit seau bleu attend près du sac. Une pomme verte brille sur la commode. Elle est froide, un peu lisse. On met la pomme dans le sac. C'est ce que l'adulte a dit. La pomme, papa. Sarah prend la pomme. Elle sent le sucre. Elle la pose tout doux, dans le sac. Bravo. La pomme est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah ferme le sac. Zzz, puis clic. La commode n'a plus sa pomme verte. Merci, Sarah. Tu as fait du bon travail. La pomme et le seau se touchent, tout frais. Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14488,7 +15292,23 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense aux balançoires, dans sa chambre.
+narrateur|Le petit seau bleu attend près du sac.
+narrateur|Une pomme verte brille sur la commode.
+narrateur|Elle est froide, un peu lisse.
+papa|On met la pomme dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|La pomme, papa.
+narrateur|Sarah prend la pomme. Elle sent le sucre.
+narrateur|Elle la pose tout doux, dans le sac.
+maman|Bravo. La pomme est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah ferme le sac. Zzz, puis clic.
+narrateur|La commode n'a plus sa pomme verte.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|La pomme et le seau se touchent, tout frais.
+narrateur|Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14516,7 +15336,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé aux balançoires. Sarah a mis le seau dans le sac. Sarah a mis la pomme aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. Un rayon reste sur la commode, vide. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14656,7 +15476,16 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé aux balançoires.
+narrateur|Sarah a mis le seau dans le sac.
+narrateur|Sarah a mis la pomme aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Un rayon reste sur la commode, vide.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14684,7 +15513,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Sarah pense aux balançoires, dans sa chambre. Le doudou beige attend sur l'oreiller. Le doudou sent le lit, encore chaud. Le doudou, maman. D'accord. On le met dans le sac. C'est ce que l'adulte a dit. Sarah glisse le doudou. Le tissu frotte, tout doux. Une oreille dépasse, puis rentre. Bravo. Le doudou est dedans. Tu as mis ce que j'ai dit ? Oui. Dans le sac. Le sac devient un peu plus lourd, un peu plus doux. La chaussette jaune ne dit rien, sur la lampe.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14824,7 +15653,19 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : mettre dans le sac. Zoé répète tout bas : sac, ce que l'adulte a dit. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>narrateur|Sarah pense aux balançoires, dans sa chambre.
+narrateur|Le doudou beige attend sur l'oreiller.
+narrateur|Le doudou sent le lit, encore chaud.
+enfant-f|Le doudou, maman.
+maman|D'accord. On le met dans le sac.
+papa|C'est ce que l'adulte a dit.
+narrateur|Sarah glisse le doudou. Le tissu frotte, tout doux.
+narrateur|Une oreille dépasse, puis rentre.
+papa|Bravo. Le doudou est dedans.
+maman|Tu as mis ce que j'ai dit ?
+enfant-f|Oui. Dans le sac.
+narrateur|Le sac devient un peu plus lourd, un peu plus doux.
+narrateur|La chaussette jaune ne dit rien, sur la lampe.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14852,7 +15693,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On met encore quoi ? Le livre, le pull, ou la pomme ? On met dans le sac. Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15020,7 +15861,10 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On met encore quoi ?
+papa|Le livre, le pull, ou la pomme ?
+maman|On met dans le sac.
+maman|Ce que l'adulte a dit.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15048,7 +15892,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense aux balançoires, dans sa chambre. Le doudou beige attend sur l'oreiller. Le petit livre a une couverture rouge. Les pages sentent le papier. On met le livre dans le sac. C'est ce que l'adulte a dit. Le livre, papa. Sarah prend le livre. Il est lisse, un peu froid. Elle le glisse à côté, dans le sac. Bravo. Le livre est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah appuie sur la fermeture. Zzz. Le sac rouge est fermé, un peu bosselé. Merci, Sarah. Tu as fait du bon travail. Le doudou et le livre se parlent tout bas. L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15188,7 +16032,23 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Tom. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense aux balançoires, dans sa chambre.
+narrateur|Le doudou beige attend sur l'oreiller.
+narrateur|Le petit livre a une couverture rouge.
+narrateur|Les pages sentent le papier.
+papa|On met le livre dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|Le livre, papa.
+narrateur|Sarah prend le livre. Il est lisse, un peu froid.
+narrateur|Elle le glisse à côté, dans le sac.
+maman|Bravo. Le livre est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah appuie sur la fermeture. Zzz.
+narrateur|Le sac rouge est fermé, un peu bosselé.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le doudou et le livre se parlent tout bas.
+narrateur|L'oiseau en papier tourne encore, tout blanc.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15216,7 +16076,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé aux balançoires. Sarah a mis le doudou dans le sac. Sarah a mis le livre aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. L'oiseau en papier tourne encore, tout blanc. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15356,7 +16216,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé aux balançoires.
+narrateur|Sarah a mis le doudou dans le sac.
+narrateur|Sarah a mis le livre aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|L'oiseau en papier tourne encore, tout blanc.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15384,7 +16253,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense aux balançoires, dans sa chambre. Le doudou beige attend sur l'oreiller. Le pull à étoile attend sur la chaise. La laine est un peu rêche, un peu chaude. On met le pull dans le sac. C'est ce que l'adulte a dit. Le pull, maman. Sarah plie le pull, comme papa. L'étoile disparaît dans le sac rouge. Bravo. Le pull est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah tire la sangle. Clic. Le sac est plus lourd, tout prêt. Merci, Sarah. Tu as fait du bon travail. Le doudou a un pull pour oreiller, dans le sac. La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15524,7 +16393,23 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Léa. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense aux balançoires, dans sa chambre.
+narrateur|Le doudou beige attend sur l'oreiller.
+narrateur|Le pull à étoile attend sur la chaise.
+narrateur|La laine est un peu rêche, un peu chaude.
+maman|On met le pull dans le sac.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le pull, maman.
+narrateur|Sarah plie le pull, comme papa.
+narrateur|L'étoile disparaît dans le sac rouge.
+papa|Bravo. Le pull est dedans.
+maman|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah tire la sangle. Clic.
+narrateur|Le sac est plus lourd, tout prêt.
+papa|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le doudou a un pull pour oreiller, dans le sac.
+narrateur|La chaise est vide, maintenant.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15552,7 +16437,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé aux balançoires. Sarah a mis le doudou dans le sac. Sarah a mis le pull aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. La chaise est vide. L'étoile est partie. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15692,7 +16577,16 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé aux balançoires.
+narrateur|Sarah a mis le doudou dans le sac.
+narrateur|Sarah a mis le pull aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|La chaise est vide. L'étoile est partie.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15720,7 +16614,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>Sarah pense aux balançoires, dans sa chambre. Le doudou beige attend sur l'oreiller. Une pomme verte brille sur la commode. Elle est froide, un peu lisse. On met la pomme dans le sac. C'est ce que l'adulte a dit. La pomme, papa. Sarah prend la pomme. Elle sent le sucre. Elle la pose tout doux, dans le sac. Bravo. La pomme est dedans. Tu as fini de préparer le sac ? Oui. Il est prêt. Sarah ferme le sac. Zzz, puis clic. La commode n'a plus sa pomme verte. Merci, Sarah. Tu as fait du bon travail. Le doudou garde la pomme, comme un secret. Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15860,7 +16754,23 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Sami. Zoé a appris : Préparer son sac. Voici le geste : mettre dans le sac. Zoé a entendu : sac, ce que l'adulte a dit. Zoé dit merci à maman. On rentre.</t>
+          <t>narrateur|Sarah pense aux balançoires, dans sa chambre.
+narrateur|Le doudou beige attend sur l'oreiller.
+narrateur|Une pomme verte brille sur la commode.
+narrateur|Elle est froide, un peu lisse.
+papa|On met la pomme dans le sac.
+maman|C'est ce que l'adulte a dit.
+enfant-f|La pomme, papa.
+narrateur|Sarah prend la pomme. Elle sent le sucre.
+narrateur|Elle la pose tout doux, dans le sac.
+maman|Bravo. La pomme est dedans.
+papa|Tu as fini de préparer le sac ?
+enfant-f|Oui. Il est prêt.
+narrateur|Sarah ferme le sac. Zzz, puis clic.
+narrateur|La commode n'a plus sa pomme verte.
+maman|Merci, Sarah. Tu as fait du bon travail.
+narrateur|Le doudou garde la pomme, comme un secret.
+narrateur|Un rayon reste sur la commode, vide.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15888,7 +16798,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a pensé aux balançoires. Sarah a mis le doudou dans le sac. Sarah a mis la pomme aussi. C'est ce que l'adulte a dit. Le sac est prêt. Oui. Bravo, Sarah. Tu as fait du bon travail. Un rayon reste sur la commode, vide. La chaussette jaune dort encore sur la lampe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16028,7 +16938,16 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah a pensé aux balançoires.
+narrateur|Sarah a mis le doudou dans le sac.
+narrateur|Sarah a mis la pomme aussi.
+papa|C'est ce que l'adulte a dit.
+enfant-f|Le sac est prêt.
+maman|Oui. Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|Un rayon reste sur la commode, vide.
+narrateur|La chaussette jaune dort encore sur la lampe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16050,7 +16969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16144,6 +17063,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-036.xlsx
+++ b/stories/arbres/TREE-AUT-036.xlsx
@@ -2562,17 +2562,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+          <t>Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -2732,7 +2732,7 @@
         <is>
           <t>narrateur|Sarah pose le ballon, sans frapper.
 papa|Le banc, la grille, ou le cerisier ?
-maman|Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+maman|Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
     </row>
@@ -2759,17 +2759,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Le banc du parc est frais, strié. Sarah y pose le sac, ouvert. Le ballon reste dans le sable, loin. Je pourrais le pousser. Elle retient sa main. Personne ne dit le geste. Elle regarde la virgule bleue. Un grain tombe, tout seul. L'aile se déplie, sans elle. Il a choisi le bois, on dirait. Il s'ouvre. Le cuir du ballon a du sable, au loin.</t>
+          <t>Le banc du parc est frais, strié. Sarah y pose le sac, ouvert. Le ballon reste dans le sable, loin. Je pourrais le pousser. Elle retient sa main. Le banc ne dit rien. Elle regarde la virgule bleue. Un grain tombe, tout seul. L'aile se déplie, sans elle. Il a choisi le bois, on dirait. Il s'ouvre. Le cuir du ballon a du sable, au loin.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;banc&lt;/emphasis&gt; du parc est frais, strié. Sarah y pose le sac, ouvert. Le ballon reste dans le sable, loin. Je pourrais le pousser. Elle retient sa main. Personne ne dit le geste. Elle regarde la virgule bleue. Un grain tombe, tout seul. L'aile se déplie, sans elle. Il a choisi le bois, on dirait. Il s'ouvre. Le cuir du ballon a du sable, au loin.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;banc&lt;/emphasis&gt; du parc est frais, strié. Sarah y pose le sac, ouvert. Le ballon reste dans le sable, loin. Je pourrais le pousser. Elle retient sa main. Le banc ne dit rien. Elle regarde la virgule bleue. Un grain tombe, tout seul. L'aile se déplie, sans elle. Il a choisi le bois, on dirait. Il s'ouvre. Le cuir du ballon a du sable, au loin.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;banc&lt;/emphasis&gt; du parc est frais, strié. Sarah y pose le sac, ouvert. Le ballon reste dans le sable, loin. Je pourrais le pousser. Elle retient sa main. Personne ne dit le geste. Elle regarde la virgule bleue. Un grain tombe, tout seul. L'aile se déplie, sans elle. Il a choisi le bois, on dirait. Il s'ouvre. Le cuir du ballon a du sable, au loin. [pause]</t>
+          <t>Le &lt;emphasis&gt;banc&lt;/emphasis&gt; du parc est frais, strié. Sarah y pose le sac, ouvert. Le ballon reste dans le sable, loin. Je pourrais le pousser. Elle retient sa main. Le banc ne dit rien. Elle regarde la virgule bleue. Un grain tombe, tout seul. L'aile se déplie, sans elle. Il a choisi le bois, on dirait. Il s'ouvre. Le cuir du ballon a du sable, au loin. [pause]</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -2908,7 +2908,7 @@
 narrateur|Le ballon reste dans le sable, loin.
 enfant-f|Je pourrais le pousser.
 narrateur|Elle retient sa main.
-narrateur|Personne ne dit le geste.
+narrateur|Le banc ne dit rien.
 narrateur|Elle regarde la virgule bleue.
 narrateur|Un grain tombe, tout seul.
 narrateur|L'aile se déplie, sans elle.
@@ -3131,17 +3131,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>La grille du parc est verte, froide. Sarah tient le sac près des barres. Le ballon roule, presque contre. Je pourrais le caler là. Elle recule le cuir, nette. Le vent passe entre deux barres. La virgule bleue se tourne vers lui. L'oiseau penche, sans main. Le vent de la grille, pas celui du ballon. Il a compris le trou. Une feuille coincée tremble, puis se tait. Le sac reste ouvert, contre rien.</t>
+          <t>La grille du parc est verte, froide. Sarah tient le sac près des barres. Le ballon roule, presque contre. Je pourrais le caler là. Elle recule le cuir, nette. Le vent passe entre deux barres. La virgule bleue se tourne vers lui. L'oiseau penche, sans main. Le vent de la grille, pas celui du ballon. Il a vu le trou. Une feuille coincée tremble, puis se tait. Le sac reste ouvert, contre rien.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;grille&lt;/emphasis&gt; du parc est verte, froide. Sarah tient le sac près des barres. Le ballon roule, presque contre. Je pourrais le caler là. Elle recule le cuir, nette. Le vent passe entre deux barres. La virgule bleue se tourne vers lui. L'oiseau penche, sans main. Le vent de la grille, pas celui du ballon. Il a compris le trou. Une feuille coincée tremble, puis se tait. Le sac reste ouvert, contre rien.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;grille&lt;/emphasis&gt; du parc est verte, froide. Sarah tient le sac près des barres. Le ballon roule, presque contre. Je pourrais le caler là. Elle recule le cuir, nette. Le vent passe entre deux barres. La virgule bleue se tourne vers lui. L'oiseau penche, sans main. Le vent de la grille, pas celui du ballon. Il a vu le trou. Une feuille coincée tremble, puis se tait. Le sac reste ouvert, contre rien.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;grille&lt;/emphasis&gt; du parc est verte, froide. Sarah tient le sac près des barres. Le ballon roule, presque contre. Je pourrais le caler là. Elle recule le cuir, nette. Le vent passe entre deux barres. La virgule bleue se tourne vers lui. L'oiseau penche, sans main. Le vent de la grille, pas celui du ballon. Il a compris le trou. Une feuille coincée tremble, puis se tait. Le sac reste ouvert, contre rien. [pause]</t>
+          <t>La &lt;emphasis&gt;grille&lt;/emphasis&gt; du parc est verte, froide. Sarah tient le sac près des barres. Le ballon roule, presque contre. Je pourrais le caler là. Elle recule le cuir, nette. Le vent passe entre deux barres. La virgule bleue se tourne vers lui. L'oiseau penche, sans main. Le vent de la grille, pas celui du ballon. Il a vu le trou. Une feuille coincée tremble, puis se tait. Le sac reste ouvert, contre rien. [pause]</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -3284,7 +3284,7 @@
 narrateur|La virgule bleue se tourne vers lui.
 narrateur|L'oiseau penche, sans main.
 maman|Le vent de la grille, pas celui du ballon.
-enfant-f|Il a compris le trou.
+enfant-f|Il a vu le trou.
 narrateur|Une feuille coincée tremble, puis se tait.
 narrateur|Le sac reste ouvert, contre rien.</t>
         </is>
@@ -4067,17 +4067,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+          <t>Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -4237,7 +4237,7 @@
         <is>
           <t>narrateur|Sarah pose le seau, sans verser.
 papa|Le banc, la grille, ou le cerisier ?
-maman|Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+maman|Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
     </row>
@@ -5195,17 +5195,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Ils rentrent, une pétale au bord du tissu. Tu raconteras le moment difficile ? Surtout quand j'ai voulu verser. L'arbre n'avait pas besoin du seau. Sarah pose le sac au pied du lit. Les sangles du sac sentent le bois, un peu.</t>
+          <t>Ils rentrent, une pétale au bord du tissu. Tu raconteras le moment difficile ? Surtout quand j'ai voulu verser. L'arbre n'avait pas besoin du seau. Sarah pose le sac au pied du lit. Les sangles du sac sentent la feuille, un peu.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils rentrent, une pétale au bord du tissu. Tu raconteras le moment difficile ? Surtout quand j'ai voulu verser. L'arbre n'avait pas besoin du seau. Sarah pose le sac au pied du lit. Les sangles du sac sentent le bois, un peu.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils rentrent, une pétale au bord du tissu. Tu raconteras le moment difficile ? Surtout quand j'ai voulu verser. L'arbre n'avait pas besoin du seau. Sarah pose le sac au pied du lit. Les sangles du sac sentent la feuille, un peu.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils rentrent, une pétale au bord du tissu. Tu raconteras le moment difficile ? Surtout quand j'ai voulu verser. L'arbre n'avait pas besoin du seau. Sarah pose le sac au pied du lit. Les sangles du sac sentent le bois, un peu.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils rentrent, une pétale au bord du tissu. Tu raconteras le moment difficile ? Surtout quand j'ai voulu verser. L'arbre n'avait pas besoin du seau. Sarah pose le sac au pied du lit. Les sangles du sac sentent la feuille, un peu.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -5348,7 +5348,7 @@
 enfant-f|Surtout quand j'ai voulu verser.
 maman|L'arbre n'avait pas besoin du seau.
 narrateur|Sarah pose le sac au pied du lit.
-narrateur|Les sangles du sac sentent le bois, un peu.</t>
+narrateur|Les sangles du sac sentent la feuille, un peu.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+          <t>Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -5742,7 +5742,7 @@
         <is>
           <t>narrateur|Sarah pose le doudou, sans serrer.
 papa|Le banc, la grille, ou le cerisier ?
-maman|Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+maman|Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
     </row>
@@ -7837,17 +7837,17 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+          <t>Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -8007,7 +8007,7 @@
         <is>
           <t>narrateur|Sarah pose le ballon, sans frapper.
 papa|Le banc, la grille, ou le cerisier ?
-maman|Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+maman|Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
     </row>
@@ -9342,17 +9342,17 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+          <t>Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -9512,7 +9512,7 @@
         <is>
           <t>narrateur|Sarah pose le seau, sans verser.
 papa|Le banc, la grille, ou le cerisier ?
-maman|Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+maman|Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
     </row>
@@ -10847,17 +10847,17 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+          <t>Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -11017,7 +11017,7 @@
         <is>
           <t>narrateur|Sarah pose le doudou, sans serrer.
 papa|Le banc, la grille, ou le cerisier ?
-maman|Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+maman|Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
     </row>
@@ -11603,17 +11603,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Ils rentrent, une goutte sèche sur le gris. Tu raconteras le moment difficile ? Surtout le tapis de pente. La grille a soufflé, sans étouffer. Sarah pose le sac, un peu ouvert. Le seau pose son ombre ronde sur le tapis.</t>
+          <t>Ils rentrent, une goutte sèche sur le gris. Tu raconteras le moment difficile ? Surtout le tapis de pente. La grille a soufflé, sans étouffer. Sarah pose le sac, un peu ouvert. L'oreille du doudou garde une goutte de métal.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils rentrent, une goutte sèche sur le gris. Tu raconteras le moment difficile ? Surtout le tapis de pente. La &lt;emphasis level="moderate"&gt;grille&lt;/emphasis&gt; a soufflé, sans étouffer. Sarah pose le sac, un peu ouvert. Le seau pose son ombre ronde sur le tapis.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils rentrent, une goutte sèche sur le gris. Tu raconteras le moment difficile ? Surtout le tapis de pente. La &lt;emphasis level="moderate"&gt;grille&lt;/emphasis&gt; a soufflé, sans étouffer. Sarah pose le sac, un peu ouvert. L'oreille du doudou garde une goutte de métal.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils rentrent, une goutte sèche sur le gris. Tu raconteras le moment difficile ? Surtout le tapis de pente. La &lt;emphasis&gt;grille&lt;/emphasis&gt; a soufflé, sans étouffer. Sarah pose le sac, un peu ouvert. Le seau pose son ombre ronde sur le tapis.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils rentrent, une goutte sèche sur le gris. Tu raconteras le moment difficile ? Surtout le tapis de pente. La &lt;emphasis&gt;grille&lt;/emphasis&gt; a soufflé, sans étouffer. Sarah pose le sac, un peu ouvert. L'oreille du doudou garde une goutte de métal.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -11756,7 +11756,7 @@
 enfant-f|Surtout le tapis de pente.
 maman|La grille a soufflé, sans étouffer.
 narrateur|Sarah pose le sac, un peu ouvert.
-narrateur|Le seau pose son ombre ronde sur le tapis.</t>
+narrateur|L'oreille du doudou garde une goutte de métal.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -11975,17 +11975,17 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Ils rentrent, un toit de feuilles dans la tête. Tu raconteras le moment difficile ? Surtout le nœud trop haut. La branche tenait, sans doudou. Sarah pose le sac au pied du lit. Le ballon s'endort contre les sangles molles.</t>
+          <t>Ils rentrent, un toit de feuilles dans la tête. Tu raconteras le moment difficile ? Surtout le nœud trop haut. La branche tenait, sans doudou. Sarah pose le sac au pied du lit. Une pétale sèche sur l'oreille du doudou.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils rentrent, un toit de feuilles dans la tête. Tu raconteras le moment difficile ? Surtout le nœud trop haut. La branche tenait, sans doudou. Sarah pose le sac au pied du lit. Le ballon s'endort contre les sangles molles.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils rentrent, un toit de feuilles dans la tête. Tu raconteras le moment difficile ? Surtout le nœud trop haut. La branche tenait, sans doudou. Sarah pose le sac au pied du lit. Une pétale sèche sur l'oreille du doudou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils rentrent, un toit de feuilles dans la tête. Tu raconteras le moment difficile ? Surtout le nœud trop haut. La branche tenait, sans doudou. Sarah pose le sac au pied du lit. Le ballon s'endort contre les sangles molles.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils rentrent, un toit de feuilles dans la tête. Tu raconteras le moment difficile ? Surtout le nœud trop haut. La branche tenait, sans doudou. Sarah pose le sac au pied du lit. Une pétale sèche sur l'oreille du doudou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -12128,7 +12128,7 @@
 enfant-f|Surtout le nœud trop haut.
 maman|La branche tenait, sans doudou.
 narrateur|Sarah pose le sac au pied du lit.
-narrateur|Le ballon s'endort contre les sangles molles.</t>
+narrateur|Une pétale sèche sur l'oreille du doudou.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
@@ -13112,17 +13112,17 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+          <t>Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Sarah pose le ballon, sans frapper. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -13282,7 +13282,7 @@
         <is>
           <t>narrateur|Sarah pose le ballon, sans frapper.
 papa|Le banc, la grille, ou le cerisier ?
-maman|Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+maman|Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
     </row>
@@ -13496,17 +13496,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Ils rentrent, la chaîne loin derrière. Tu raconteras le moment difficile ? Surtout le tic sur le sac. Le banc n'a pas tapé. Sarah pose le sac au pied du lit. Une pétale sèche sur le rebord, près du livre.</t>
+          <t>Ils rentrent, la chaîne loin derrière. Tu raconteras le moment difficile ? Surtout le tic sur le sac. Le banc n'a pas tapé. Sarah pose le sac au pied du lit. Le ballon s'endort contre les sangles molles.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils rentrent, la chaîne loin derrière. Tu raconteras le moment difficile ? Surtout le tic sur le sac. Le &lt;emphasis level="moderate"&gt;banc&lt;/emphasis&gt; n'a pas tapé. Sarah pose le sac au pied du lit. Une pétale sèche sur le rebord, près du livre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils rentrent, la chaîne loin derrière. Tu raconteras le moment difficile ? Surtout le tic sur le sac. Le &lt;emphasis level="moderate"&gt;banc&lt;/emphasis&gt; n'a pas tapé. Sarah pose le sac au pied du lit. Le ballon s'endort contre les sangles molles.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils rentrent, la chaîne loin derrière. Tu raconteras le moment difficile ? Surtout le tic sur le sac. Le &lt;emphasis&gt;banc&lt;/emphasis&gt; n'a pas tapé. Sarah pose le sac au pied du lit. Une pétale sèche sur le rebord, près du livre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils rentrent, la chaîne loin derrière. Tu raconteras le moment difficile ? Surtout le tic sur le sac. Le &lt;emphasis&gt;banc&lt;/emphasis&gt; n'a pas tapé. Sarah pose le sac au pied du lit. Le ballon s'endort contre les sangles molles.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -13649,7 +13649,7 @@
 enfant-f|Surtout le tic sur le sac.
 maman|Le banc n'a pas tapé.
 narrateur|Sarah pose le sac au pied du lit.
-narrateur|Une pétale sèche sur le rebord, près du livre.</t>
+narrateur|Le ballon s'endort contre les sangles molles.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
@@ -14617,17 +14617,17 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+          <t>Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Sarah pose le seau, sans verser. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -14787,7 +14787,7 @@
         <is>
           <t>narrateur|Sarah pose le seau, sans verser.
 papa|Le banc, la grille, ou le cerisier ?
-maman|Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+maman|Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
     </row>
@@ -16122,17 +16122,17 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+          <t>Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où l'oiseau peut-il s'ouvrir tout seul ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Sarah pose le doudou, sans serrer. Le banc, la grille, ou le cerisier ? Où poses-tu le sac, ouvert ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -16292,7 +16292,7 @@
         <is>
           <t>narrateur|Sarah pose le doudou, sans serrer.
 papa|Le banc, la grille, ou le cerisier ?
-maman|Où l'oiseau peut-il s'ouvrir tout seul ?</t>
+maman|Où poses-tu le sac, ouvert ?</t>
         </is>
       </c>
     </row>
@@ -17429,7 +17429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17542,6 +17542,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
